--- a/data/trans_orig/IP16B02-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP16B02-Estudios-trans_orig.xlsx
@@ -732,7 +732,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3718</t>
+          <t>3115</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>5258</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10860</t>
+          <t>10477</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15676</t>
+          <t>15635</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>66,66%</t>
+          <t>64,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>95,96%</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3237</t>
+          <t>3840</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>55,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4052</t>
+          <t>4080</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>658</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5433</t>
+          <t>5816</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>35,7%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16466</t>
+          <t>16607</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23641</t>
+          <t>23731</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>63,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24272</t>
+          <t>24673</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30141</t>
+          <t>30193</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>78,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>43927</t>
+          <t>43639</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52572</t>
+          <t>52668</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,28%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2712</t>
+          <t>2622</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9887</t>
+          <t>9746</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>36,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1208</t>
+          <t>1156</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7077</t>
+          <t>6676</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>5034</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13775</t>
+          <t>14063</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>24,37%</t>
         </is>
       </c>
     </row>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3794</t>
+          <t>3729</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>51,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12449</t>
+          <t>12160</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16659</t>
+          <t>16650</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>70,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17262</t>
+          <t>18150</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23400</t>
+          <t>23451</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>70,14%</t>
+          <t>73,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,29%</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3505</t>
+          <t>3570</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>48,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>661</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4862</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>1159</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7348</t>
+          <t>6460</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>26,25%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27316</t>
+          <t>27806</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36076</t>
+          <t>36010</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>68,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>47118</t>
+          <t>46813</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54675</t>
+          <t>54589</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>80,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>77266</t>
+          <t>77913</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>88783</t>
+          <t>89306</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>90,57%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4531</t>
+          <t>4597</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13291</t>
+          <t>12801</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3323</t>
+          <t>3409</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10880</t>
+          <t>11185</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9822</t>
+          <t>9299</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>21339</t>
+          <t>20692</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>20,99%</t>
         </is>
       </c>
     </row>
@@ -2335,12 +2335,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4523</t>
+          <t>4617</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9086</t>
+          <t>9109</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>47,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4347</t>
+          <t>4040</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>49,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10991</t>
+          <t>10552</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16640</t>
+          <t>16474</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>58,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>91,87%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>677</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5263</t>
+          <t>5169</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>52,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3800</t>
+          <t>4107</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>50,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>1459</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6942</t>
+          <t>7381</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>41,16%</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34845</t>
+          <t>34943</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44640</t>
+          <t>45035</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>67,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>42142</t>
+          <t>42059</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49687</t>
+          <t>49666</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>80,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>80554</t>
+          <t>80339</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>92504</t>
+          <t>92271</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>88,65%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>6758</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16948</t>
+          <t>16850</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2607</t>
+          <t>2628</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10152</t>
+          <t>10235</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>11583</t>
+          <t>11816</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>23533</t>
+          <t>23748</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,82%</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13138</t>
+          <t>13317</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8490</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13488</t>
+          <t>13479</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>60,08%</t>
+          <t>58,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23564</t>
+          <t>23562</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30016</t>
+          <t>29969</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>75,37%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>95,86%</t>
         </is>
       </c>
     </row>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3994</t>
+          <t>3815</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>653</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5642</t>
+          <t>5861</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1248</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7700</t>
+          <t>7702</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,64%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>57051</t>
+          <t>57235</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>68588</t>
+          <t>68961</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>72,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>59559</t>
+          <t>59379</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>69537</t>
+          <t>69492</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>121270</t>
+          <t>120894</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>136264</t>
+          <t>135732</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>88,55%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10123</t>
+          <t>9750</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21660</t>
+          <t>21476</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5036</t>
+          <t>5081</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15014</t>
+          <t>15194</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>17020</t>
+          <t>17552</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>32014</t>
+          <t>32390</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,13%</t>
         </is>
       </c>
     </row>
@@ -3938,12 +3938,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1546</t>
+          <t>1759</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5505</t>
+          <t>5930</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>88,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6347</t>
+          <t>6454</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11481</t>
+          <t>11480</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4023,12 +4023,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>51,73%</t>
+          <t>52,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,56%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1199</t>
+          <t>774</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5158</t>
+          <t>4945</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>73,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>789</t>
+          <t>790</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5923</t>
+          <t>5816</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>47,4%</t>
         </is>
       </c>
     </row>
@@ -4281,12 +4281,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30868</t>
+          <t>30616</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37452</t>
+          <t>37160</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4296,12 +4296,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>78,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4316,12 +4316,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22885</t>
+          <t>23091</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28892</t>
+          <t>28895</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4331,12 +4331,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>75,99%</t>
+          <t>76,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>56813</t>
+          <t>56526</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>65170</t>
+          <t>64934</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>93,89%</t>
         </is>
       </c>
     </row>
@@ -4394,12 +4394,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1595</t>
+          <t>1887</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8179</t>
+          <t>8431</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1222</t>
+          <t>1219</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7229</t>
+          <t>7023</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3991</t>
+          <t>4227</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>12348</t>
+          <t>12635</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>18,27%</t>
         </is>
       </c>
     </row>
@@ -4624,12 +4624,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9649</t>
+          <t>9484</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14895</t>
+          <t>15006</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>58,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4659,7 +4659,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11802</t>
+          <t>11805</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -4674,7 +4674,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>73,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -4694,12 +4694,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23339</t>
+          <t>23848</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30301</t>
+          <t>30346</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4709,12 +4709,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,17%</t>
         </is>
       </c>
     </row>
@@ -4737,12 +4737,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1328</t>
+          <t>1217</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6574</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>41,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4777,7 +4777,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4198</t>
+          <t>4195</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4792,7 +4792,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1922</t>
+          <t>1877</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8884</t>
+          <t>8375</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4822,12 +4822,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>25,99%</t>
         </is>
       </c>
     </row>
@@ -4967,12 +4967,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45684</t>
+          <t>45988</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>55848</t>
+          <t>55696</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>74,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43068</t>
+          <t>42480</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49505</t>
+          <t>49702</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>91854</t>
+          <t>91907</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>103806</t>
+          <t>103862</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5052,12 +5052,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>80,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,38%</t>
         </is>
       </c>
     </row>
@@ -5080,12 +5080,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6127</t>
+          <t>6279</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16291</t>
+          <t>15987</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5115,12 +5115,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2174</t>
+          <t>1977</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8611</t>
+          <t>9199</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9848</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>21800</t>
+          <t>21747</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5165,12 +5165,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,13%</t>
         </is>
       </c>
     </row>
